--- a/SMART RSA-RCS Testing Datasets.xlsx
+++ b/SMART RSA-RCS Testing Datasets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\Responsive Services or RCS\Conceptualization\FESA RSA RCS PACKAGE PROJECTS\SMART RSA RCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1928883B-4B4A-41E4-817F-716ED21545BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB627CF2-3DD2-452A-98C5-7135D93C83A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="90">
   <si>
     <t>RSA No</t>
   </si>
@@ -282,19 +282,25 @@
     <t>Active-Linked</t>
   </si>
   <si>
-    <t>Dediczted centre</t>
-  </si>
-  <si>
-    <t>No dedicted cebtre</t>
-  </si>
-  <si>
     <t>DS  Centre QOO Testing Status</t>
   </si>
   <si>
-    <t>Dedicted cebtre</t>
-  </si>
-  <si>
-    <t>No dediczted centre</t>
+    <t>Explanation of terms</t>
+  </si>
+  <si>
+    <t>QOS: Quality of Service</t>
+  </si>
+  <si>
+    <t>QOP: Quality pf Process</t>
+  </si>
+  <si>
+    <t>QOO: Quality of Outcome</t>
+  </si>
+  <si>
+    <t>QODIL: Quality of Deep Interaction Linking</t>
+  </si>
+  <si>
+    <t>Dedicated Centre</t>
   </si>
 </sst>
 </file>
@@ -654,17 +660,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="13" max="13" width="15.21875" customWidth="1"/>
-    <col min="14" max="15" width="14.77734375" customWidth="1"/>
+    <col min="14" max="14" width="14.77734375" customWidth="1"/>
+    <col min="15" max="15" width="28.44140625" customWidth="1"/>
     <col min="17" max="17" width="14.6640625" customWidth="1"/>
     <col min="18" max="18" width="23" customWidth="1"/>
   </cols>
@@ -952,6 +959,31 @@
       </c>
       <c r="P6" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -964,17 +996,19 @@
   <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.77734375" customWidth="1"/>
     <col min="13" max="13" width="15.21875" customWidth="1"/>
     <col min="14" max="14" width="14.77734375" customWidth="1"/>
-    <col min="15" max="17" width="32.44140625" customWidth="1"/>
+    <col min="15" max="15" width="27.77734375" customWidth="1"/>
+    <col min="16" max="17" width="32.44140625" customWidth="1"/>
     <col min="18" max="18" width="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1277,16 +1311,17 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26.109375" customWidth="1"/>
+    <col min="9" max="9" width="16.88671875" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.77734375" customWidth="1"/>
     <col min="13" max="13" width="15.21875" customWidth="1"/>
     <col min="14" max="14" width="14.77734375" customWidth="1"/>
-    <col min="15" max="15" width="29.44140625" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" customWidth="1"/>
     <col min="17" max="17" width="14.6640625" customWidth="1"/>
     <col min="18" max="18" width="23" customWidth="1"/>
   </cols>
@@ -1698,7 +1733,7 @@
         <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="P2" t="s">
         <v>13</v>
@@ -1745,7 +1780,7 @@
         <v>40</v>
       </c>
       <c r="O3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="P3" t="s">
         <v>13</v>
@@ -1792,7 +1827,7 @@
         <v>17</v>
       </c>
       <c r="O4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P4" t="s">
         <v>13</v>
@@ -1839,7 +1874,7 @@
         <v>17</v>
       </c>
       <c r="O5" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P5" t="s">
         <v>13</v>
@@ -1886,7 +1921,7 @@
         <v>17</v>
       </c>
       <c r="O6" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P6" t="s">
         <v>13</v>
@@ -1906,12 +1941,12 @@
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.77734375" customWidth="1"/>
     <col min="13" max="13" width="15.21875" customWidth="1"/>
-    <col min="14" max="14" width="14.77734375" customWidth="1"/>
+    <col min="14" max="14" width="19.109375" customWidth="1"/>
     <col min="15" max="15" width="31.21875" customWidth="1"/>
     <col min="17" max="17" width="19.21875" customWidth="1"/>
     <col min="18" max="18" width="23" customWidth="1"/>
@@ -1952,7 +1987,7 @@
         <v>72</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>73</v>
@@ -2011,7 +2046,7 @@
         <v>40</v>
       </c>
       <c r="O2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P2" t="s">
         <v>13</v>
@@ -2058,7 +2093,7 @@
         <v>39</v>
       </c>
       <c r="O3" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P3" t="s">
         <v>13</v>
@@ -2105,7 +2140,7 @@
         <v>17</v>
       </c>
       <c r="O4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P4" t="s">
         <v>13</v>
@@ -2152,7 +2187,7 @@
         <v>17</v>
       </c>
       <c r="O5" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P5" t="s">
         <v>13</v>
@@ -2199,7 +2234,7 @@
         <v>17</v>
       </c>
       <c r="O6" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P6" t="s">
         <v>13</v>
@@ -2224,7 +2259,8 @@
     <col min="11" max="11" width="12.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.77734375" customWidth="1"/>
     <col min="13" max="13" width="15.21875" customWidth="1"/>
-    <col min="14" max="15" width="14.77734375" customWidth="1"/>
+    <col min="14" max="14" width="14.77734375" customWidth="1"/>
+    <col min="15" max="15" width="19.109375" customWidth="1"/>
     <col min="17" max="17" width="19.21875" customWidth="1"/>
     <col min="18" max="18" width="23" customWidth="1"/>
   </cols>
@@ -2323,7 +2359,7 @@
         <v>17</v>
       </c>
       <c r="O2" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P2" t="s">
         <v>13</v>
@@ -2370,7 +2406,7 @@
         <v>17</v>
       </c>
       <c r="O3" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P3" t="s">
         <v>13</v>
@@ -2417,7 +2453,7 @@
         <v>17</v>
       </c>
       <c r="O4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P4" t="s">
         <v>13</v>
@@ -2464,7 +2500,7 @@
         <v>17</v>
       </c>
       <c r="O5" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P5" t="s">
         <v>13</v>
@@ -2511,7 +2547,7 @@
         <v>17</v>
       </c>
       <c r="O6" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="P6" t="s">
         <v>13</v>
